--- a/INVENTARIO (LICC - CIRNA) 2026 - 17082026.xlsx
+++ b/INVENTARIO (LICC - CIRNA) 2026 - 17082026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario1\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario1\Desktop\inventrio de del proyecto de analisi de alimentos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA98902D-5C21-4E29-9FA3-F96B31F837F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A260F7-7843-404F-BFE5-FFC4046D3823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12090" yWindow="0" windowWidth="8505" windowHeight="10905" firstSheet="8" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SOLVENTES" sheetId="10" r:id="rId1"/>
@@ -5205,6 +5205,8 @@
     <col min="2" max="2" width="29.7109375" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" customWidth="1"/>
     <col min="4" max="4" width="16.5703125" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="21.28515625" customWidth="1"/>
     <col min="11" max="11" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
